--- a/reports/一级子公司A_利润表_2026-03.xlsx
+++ b/reports/一级子公司A_利润表_2026-03.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>151572541</v>
+        <v>155485227</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>147042631</v>
+        <v>147034047</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>449528077</v>
+        <v>448711150</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>699703</v>
+        <v>704050</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1933313</v>
+        <v>1939464</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>609139</v>
+        <v>610373</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1677383</v>
+        <v>1683937</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>515095</v>
+        <v>516462</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1421214</v>
+        <v>1427085</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>472692</v>
+        <v>474181</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1307646</v>
+        <v>1312056</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>257659</v>
+        <v>257123</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>710800</v>
+        <v>712153</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>206450</v>
+        <v>205295</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>568551</v>
+        <v>568796</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>148811803</v>
+        <v>152717743</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>144281893</v>
+        <v>144266563</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>62337385</v>
+        <v>61954096</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>215500307</v>
+        <v>214851576</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1597473</v>
+        <v>1589459</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>4406092</v>
+        <v>4387926</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1438455</v>
+        <v>1439784</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>3979568</v>
+        <v>3965484</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>77192779</v>
+        <v>77533036</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>213275146</v>
+        <v>213081011</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1655410</v>
+        <v>1655015</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>4548818</v>
+        <v>4550199</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>720488</v>
+        <v>724441</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1989560</v>
+        <v>1992537</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2563509</v>
+        <v>2588927</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>7107107</v>
+        <v>7132295</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1134605</v>
+        <v>1138748</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>3127571</v>
+        <v>3138048</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4437401</v>
+        <v>4447512</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>12223350</v>
+        <v>12273315</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>92509</v>
+        <v>92917</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>265728</v>
+        <v>279197</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2348483</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>6500666</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1562268</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>4327703</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>117767839</v>
+        <v>125583977</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>105214535</v>
+        <v>104614321</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>103046265</v>
+        <v>102461420</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>284327623</v>
+        <v>283386108</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2168270</v>
+        <v>2152901</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>5969879</v>
+        <v>5946798</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>3902146</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>10759300</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1251234</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>3445077</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>783751</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>2155781</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>942376</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>2591069</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>707790</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1946607</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>472148</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1299691</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>393335</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1084209</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1801951</v>
+        <v>1809193</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>4974065</v>
+        <v>4995089</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1386632</v>
+        <v>1393111</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>3837747</v>
+        <v>3852117</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1134322</v>
+        <v>1132829</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>3127580</v>
+        <v>3135978</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>8568236</v>
+        <v>8529202</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>23594157</v>
+        <v>23628079</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>359848</v>
+        <v>359075</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1031994</v>
+        <v>994814</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>688947</v>
+        <v>686577</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>1984151</v>
+        <v>2066435</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>784800</v>
+        <v>686577</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>2249537</v>
+        <v>2066435</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>92769</v>
+        <v>92285</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>265693</v>
+        <v>277009</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>351280</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1052526</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>684469</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1884272</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>235193</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>702999</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>176735</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>528099</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>294952</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>881670</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>983654</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>2708153</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>157316</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>471416</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>117837</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>353698</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>196021</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>589301</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>136914</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>412102</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>97590</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>293924</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>77944</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>234740</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>58406</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>175768</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>31043964</v>
+        <v>29546175</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>39941505</v>
+        <v>35962920</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>390412</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1076033</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>97810</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>292594</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>154664</v>
+        <v>154770</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>443642</v>
+        <v>462578</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>30889300</v>
+        <v>29781817</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5458209</v>
+        <v>5485680</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>15687608</v>
+        <v>16399390</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>25431091</v>
+        <v>24296137</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>25431091</v>
+        <v>24296137</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>25431091</v>
+        <v>24296137</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>25431091</v>
+        <v>24296137</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>25431091</v>
+        <v>24296137</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
